--- a/output/one_schedules_2026-08-05.xlsx
+++ b/output/one_schedules_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,40 +446,50 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ETD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Vessel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Voyage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ETD</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>POD</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ETA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TransitDays</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ScrapedAt</t>
         </is>
@@ -501,24 +511,453 @@
           <t>SEGOT</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>(Parse pending)</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ONE Solutions Support English HOME SCHEDULE PRICES BOOKING DOCUMENTATION MANAGE SHIPMENT FINANCE Search Schedule Search for schedules, book, and manage your shipment. User Guide Point to Point Vessel Port Long Range List Calendar POL/ POD Selection Go Green Origin Destination Date Next 2 Weeks Cargo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:02 UTC</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>(Input error: Locator.click: Timeout 30000ms exceeded.
+Call log:
+waiting for locator("input").first.first
+  -   locator resolved to &lt;input id=":ri:" role="switch" type="checkbox" data-enabled="false" aria-labelledby=":ri:--label" class="mag-toggle__input mag-toggle__input--size-responsive mag-toggle__input--labelAlignment-left"/&gt;
+  - attempting click action
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #1
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #2
+  -   waiting 20ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #3
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #4
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #5
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #6
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #7
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #8
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #9
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #10
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #11
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #12
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #13
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #14
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #15
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #16
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #17
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #18
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #19
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #20
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #21
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #22
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #23
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #24
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #25
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #26
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #27
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #28
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #29
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #30
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #31
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #32
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #33
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #34
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #35
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #36
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #37
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #38
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #39
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #40
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #41
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #42
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #43
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #44
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #45
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #46
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #47
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #48
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #49
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #50
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #51
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #52
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #53
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #54
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #55
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #56
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #57
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #58
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #59
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #60
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #61
+  -   waiting 500ms
+)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-08-05 07:16 UTC</t>
         </is>
       </c>
     </row>
@@ -538,24 +977,460 @@
           <t>NOOSL</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>(Parse pending)</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ONE Solutions Support English HOME SCHEDULE PRICES BOOKING DOCUMENTATION MANAGE SHIPMENT FINANCE Search Schedule Search for schedules, book, and manage your shipment. User Guide Point to Point Vessel Port Long Range List Calendar POL/ POD Selection Go Green Origin HONG KONG, HONG KONG, CHINA (CY) De</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:02 UTC</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>(Input error: Locator.click: Timeout 30000ms exceeded.
+Call log:
+waiting for locator("input").first.first
+  -   locator resolved to &lt;input id=":ri:" role="switch" type="checkbox" data-enabled="false" aria-labelledby=":ri:--label" class="mag-toggle__input mag-toggle__input--size-responsive mag-toggle__input--labelAlignment-left"/&gt;
+  - attempting click action
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #1
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #2
+  -   waiting 20ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #3
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #4
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #5
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #6
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #7
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #8
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #9
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #10
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #11
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #12
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #13
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #14
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #15
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #16
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #17
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #18
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #19
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #20
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #21
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #22
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #23
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #24
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #25
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #26
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #27
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #28
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #29
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #30
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #31
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #32
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #33
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #34
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #35
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #36
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #37
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #38
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #39
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #40
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #41
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #42
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #43
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #44
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #45
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #46
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #47
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #48
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #49
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #50
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #51
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #52
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #53
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #54
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #55
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #56
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #57
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #58
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #59
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #60
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #61
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #62
+  -   waiting 500ms
+)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-08-05 07:17 UTC</t>
         </is>
       </c>
     </row>
@@ -575,24 +1450,933 @@
           <t>NOTAE</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>(Parse pending)</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ONE Solutions Support English HOME SCHEDULE PRICES BOOKING DOCUMENTATION MANAGE SHIPMENT FINANCE Search Schedule Search for schedules, book, and manage your shipment. User Guide Point to Point Vessel Port Long Range List Calendar POL/ POD Selection Go Green Origin HO CHI MINH, VIETNAM (CY) TANANGER,</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:02 UTC</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>(Input error: Locator.click: Timeout 30000ms exceeded.
+Call log:
+waiting for locator("input").first.first
+  -   locator resolved to &lt;input id=":ri:" role="switch" type="checkbox" data-enabled="false" aria-labelledby=":ri:--label" class="mag-toggle__input mag-toggle__input--size-responsive mag-toggle__input--labelAlignment-left"/&gt;
+  - attempting click action
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #1
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #2
+  -   waiting 20ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #3
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #4
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #5
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #6
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #7
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #8
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #9
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #10
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #11
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #12
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #13
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #14
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #15
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #16
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #17
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #18
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #19
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #20
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #21
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #22
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #23
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #24
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #25
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #26
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #27
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #28
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #29
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #30
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #31
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #32
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #33
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #34
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #35
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #36
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #37
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #38
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #39
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #40
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #41
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #42
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #43
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #44
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #45
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #46
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #47
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #48
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #49
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #50
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #51
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #52
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #53
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #54
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #55
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #56
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #57
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #58
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #59
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #60
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #61
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #62
+  -   waiting 500ms
+)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-08-05 07:18 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>(Input error: Locator.click: Timeout 30000ms exceeded.
+Call log:
+waiting for locator("input").first.first
+  -   locator resolved to &lt;input id=":ri:" role="switch" type="checkbox" data-enabled="false" aria-labelledby=":ri:--label" class="mag-toggle__input mag-toggle__input--size-responsive mag-toggle__input--labelAlignment-left"/&gt;
+  - attempting click action
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #1
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #2
+  -   waiting 20ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #3
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #4
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #5
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #6
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #7
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #8
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #9
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #10
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #11
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #12
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #13
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #14
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #15
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #16
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #17
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #18
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #19
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #20
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #21
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #22
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #23
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #24
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #25
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #26
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #27
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #28
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #29
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #30
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #31
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #32
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #33
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #34
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #35
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #36
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #37
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #38
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #39
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #40
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #41
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #42
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #43
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #44
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #45
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #46
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #47
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #48
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #49
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #50
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #51
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #52
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #53
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #54
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #55
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #56
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #57
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #58
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #59
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #60
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #61
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #62
+  -   waiting 500ms
+)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-08-05 07:18 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_2026-08-05.xlsx
+++ b/output/one_schedules_2026-08-05.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_2026-08-05.xlsx
+++ b/output/one_schedules_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1114,96 +1114,60 @@
           <t>NOOSL</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HONG KONG</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SX1</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ONE MAGDALENA 2630W</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ROTTERDAM</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (2)</t>
-        </is>
-      </c>
+          <t>(Error: None)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SX1</t>
-        </is>
-      </c>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO FI631A</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1177,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,49 +1192,45 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>EMMANUEL P 012S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1240,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,49 +1255,45 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>EMMANUEL P 012S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,64 +1303,60 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 016S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1366,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,49 +1381,45 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 016S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,64 +1429,60 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SX1</t>
-        </is>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SEASPAN BELIEF</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SEASPAN BELIEF 2632W</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1553,7 +1497,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,49 +1507,45 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SX1</t>
-        </is>
-      </c>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MSC SHREYA B</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MSC SHREYA B FI633A</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1620,265 +1560,265 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>YM COSMOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 186S</t>
+          <t>YM COSMOS 191E</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ONE ORINOCO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 186S</t>
+          <t>ONE ORINOCO 2630E</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ESPIRITO SANTO EXPRESS</t>
+          <t>HMM OSLO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ESPIRITO SANTO EXPRESS 2634W</t>
+          <t>HMM OSLO 020W</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>HMM OSLO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1188S</t>
+          <t>HMM OSLO 020W</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1888,525 +1828,553 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>YM MOBILITY</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1188S</t>
+          <t>YM MOBILITY 090E</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>AX3</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>TENO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>TENO 2631E</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE FUTURE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE FUTURE 009W</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE FUTURE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE FUTURE 009W</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HYUNDAI FORWARD 171E</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>AX3</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>SEASPAN ZAMBEZI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>SEASPAN ZAMBEZI 2632E</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE MODERN 082E</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HMM LE HAVRE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HMM LE HAVRE 019W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2433,22 +2401,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>YM COSMOS</t>
+          <t>HMM LE HAVRE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>YM COSMOS 191E</t>
+          <t>HMM LE HAVRE 019W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2463,7 +2431,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,7 +2441,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2468,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2510,12 +2478,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ONE ORINOCO</t>
+          <t>POSORJA EXPRESS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ONE ORINOCO 2630E</t>
+          <t>POSORJA EXPRESS 2633E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2525,12 +2493,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2540,7 +2508,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2567,22 +2535,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HMM OSLO</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HMM OSLO 020W</t>
+          <t>ONE COMPETENCE 099E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2592,12 +2560,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2607,7 +2575,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2602,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HMM OSLO</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HMM OSLO 020W</t>
+          <t>HMM VANCOUVER 307E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2659,12 +2627,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2674,7 +2642,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2701,22 +2669,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>YM MOBILITY</t>
+          <t>ONE FOREVER</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>YM MOBILITY 090E</t>
+          <t>ONE FOREVER 010W</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2726,12 +2694,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2741,7 +2709,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2736,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TENO</t>
+          <t>ONE FOREVER</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>TENO 2631E</t>
+          <t>ONE FOREVER 010W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2793,12 +2761,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2808,7 +2776,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2835,22 +2803,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ONE FUTURE</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ONE FUTURE 009W</t>
+          <t>HYUNDAI SUPREME 159E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2860,12 +2828,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2875,7 +2843,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2902,22 +2870,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ONE FUTURE</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ONE FUTURE 009W</t>
+          <t>CONTI CONTESSA 026E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2927,12 +2895,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2942,811 +2910,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>HYUNDAI FORWARD</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>HYUNDAI FORWARD 171E</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>AX3</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>SEASPAN ZAMBEZI</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>SEASPAN ZAMBEZI 2632E</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ONE MODERN</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>ONE MODERN 082E</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>HMM LE HAVRE</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>HMM LE HAVRE 019W</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>HMM LE HAVRE</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>HMM LE HAVRE 019W</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>AX3</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>POSORJA EXPRESS</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>POSORJA EXPRESS 2633E</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>ONE COMPETENCE</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>ONE COMPETENCE 099E</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>HMM VANCOUVER</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>HMM VANCOUVER 307E</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>ONE FOREVER</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>ONE FOREVER 010W</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>ONE FOREVER</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>ONE FOREVER 010W</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>HYUNDAI SUPREME</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>HYUNDAI SUPREME 159E</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>CONTI CONTESSA</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>CONTI CONTESSA 026E</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
